--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2026 artfynd.xlsx
+++ b/artfynd/A 35413-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194059</v>
       </c>
       <c r="B2" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194064</v>
       </c>
       <c r="B3" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194065</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194066</v>
       </c>
       <c r="B5" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194067</v>
       </c>
       <c r="B6" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194104</v>
       </c>
       <c r="B7" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194105</v>
       </c>
       <c r="B8" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194106</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194108</v>
       </c>
       <c r="B10" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136194118</v>
       </c>
       <c r="B11" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136194133</v>
       </c>
       <c r="B12" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136194102</v>
       </c>
       <c r="B13" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136194103</v>
       </c>
       <c r="B14" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136194107</v>
       </c>
       <c r="B15" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>136194119</v>
       </c>
       <c r="B16" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136194134</v>
       </c>
       <c r="B17" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
